--- a/data/dividends_info_20260622.xlsx
+++ b/data/dividends_info_20260622.xlsx
@@ -523,10 +523,10 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>69.69000244140625</v>
+        <v>69.38999938964844</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1291433445933223</v>
+        <v>0.1297016872627703</v>
       </c>
       <c r="J2" t="n">
         <v>266</v>
@@ -570,10 +570,10 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>65.90000152587891</v>
+        <v>66.30000305175781</v>
       </c>
       <c r="I3" t="n">
-        <v>1.06221545340194</v>
+        <v>1.055806889561585</v>
       </c>
       <c r="J3" t="n">
         <v>245</v>
@@ -617,10 +617,10 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>9.100000381469727</v>
+        <v>9.199999809265137</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6593406317012648</v>
+        <v>0.6521739265643809</v>
       </c>
       <c r="J4" t="n">
         <v>175</v>
@@ -711,10 +711,10 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>69.68000030517578</v>
+        <v>69.38999938964844</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1291618823275391</v>
+        <v>0.1297016872627703</v>
       </c>
       <c r="J6" t="n">
         <v>175</v>
@@ -758,10 +758,10 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>2.039999961853027</v>
+        <v>2.059999942779541</v>
       </c>
       <c r="I7" t="n">
-        <v>3.774509874503002</v>
+        <v>3.737864181496264</v>
       </c>
       <c r="J7" t="n">
         <v>154</v>
@@ -805,10 +805,10 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>21.60499954223633</v>
+        <v>21.57500076293945</v>
       </c>
       <c r="I8" t="n">
-        <v>1.249710741590936</v>
+        <v>1.251448391435488</v>
       </c>
       <c r="J8" t="n">
         <v>154</v>
@@ -852,10 +852,10 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>5.940000057220459</v>
+        <v>5.989999771118164</v>
       </c>
       <c r="I9" t="n">
-        <v>3.367003334568775</v>
+        <v>3.338898291187508</v>
       </c>
       <c r="J9" t="n">
         <v>147</v>
@@ -1040,10 +1040,10 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>4.980000019073486</v>
+        <v>4.96999979019165</v>
       </c>
       <c r="I13" t="n">
-        <v>0.7630522059128382</v>
+        <v>0.7645875574279384</v>
       </c>
       <c r="J13" t="n">
         <v>98</v>
@@ -1087,10 +1087,10 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>21.60499954223633</v>
+        <v>21.57500076293945</v>
       </c>
       <c r="I14" t="n">
-        <v>1.249710741590936</v>
+        <v>1.251448391435488</v>
       </c>
       <c r="J14" t="n">
         <v>91</v>
@@ -1134,10 +1134,10 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>69.68000030517578</v>
+        <v>69.38999938964844</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1291618823275391</v>
+        <v>0.1297016872627703</v>
       </c>
       <c r="J15" t="n">
         <v>91</v>
@@ -1181,10 +1181,10 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>6</v>
+        <v>5.900000095367432</v>
       </c>
       <c r="I16" t="n">
-        <v>5</v>
+        <v>5.08474568052218</v>
       </c>
       <c r="J16" t="n">
         <v>84</v>
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>4.980000019073486</v>
+        <v>4.96999979019165</v>
       </c>
       <c r="I18" t="n">
-        <v>0.7630522059128382</v>
+        <v>0.7645875574279384</v>
       </c>
       <c r="J18" t="n">
         <v>42</v>
@@ -1322,10 +1322,10 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>5.550000190734863</v>
+        <v>5.590000152587891</v>
       </c>
       <c r="I19" t="n">
-        <v>4.504504349699816</v>
+        <v>4.472271792054648</v>
       </c>
       <c r="J19" t="n">
         <v>35</v>
@@ -1416,10 +1416,10 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>9.814999580383301</v>
+        <v>9.821000099182129</v>
       </c>
       <c r="I21" t="n">
-        <v>2.649006735768463</v>
+        <v>2.647388222933143</v>
       </c>
       <c r="J21" t="n">
         <v>28</v>
@@ -1463,10 +1463,10 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>15.35999965667725</v>
+        <v>15.22000026702881</v>
       </c>
       <c r="I22" t="n">
-        <v>3.906250087311494</v>
+        <v>3.942181271177663</v>
       </c>
       <c r="J22" t="n">
         <v>28</v>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>3.644000053405762</v>
+        <v>3.589999914169312</v>
       </c>
       <c r="I23" t="n">
-        <v>6.037321536106544</v>
+        <v>6.128133851248453</v>
       </c>
       <c r="J23" t="n">
         <v>28</v>
@@ -1604,10 +1604,10 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>6.360000133514404</v>
+        <v>6.425000190734863</v>
       </c>
       <c r="I25" t="n">
-        <v>3.773584826442149</v>
+        <v>3.735408449420604</v>
       </c>
       <c r="J25" t="n">
         <v>28</v>
@@ -1651,10 +1651,10 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>18.39999961853027</v>
+        <v>18.64999961853027</v>
       </c>
       <c r="I26" t="n">
-        <v>2.04347830323506</v>
+        <v>2.016085832122022</v>
       </c>
       <c r="J26" t="n">
         <v>28</v>
@@ -1698,10 +1698,10 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>5.829999923706055</v>
+        <v>5.840000152587891</v>
       </c>
       <c r="I27" t="n">
-        <v>2.058319066387184</v>
+        <v>2.054794466860145</v>
       </c>
       <c r="J27" t="n">
         <v>21</v>
@@ -1792,10 +1792,10 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>2.819999933242798</v>
+        <v>2.740000009536743</v>
       </c>
       <c r="I29" t="n">
-        <v>5.319149062089187</v>
+        <v>5.474452535690348</v>
       </c>
       <c r="J29" t="n">
         <v>21</v>
@@ -1886,10 +1886,10 @@
         </is>
       </c>
       <c r="H31" t="n">
-        <v>4.869999885559082</v>
+        <v>4.739999771118164</v>
       </c>
       <c r="I31" t="n">
-        <v>1.437371697021383</v>
+        <v>1.476793320255521</v>
       </c>
       <c r="J31" t="n">
         <v>14</v>
@@ -1933,10 +1933,10 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>35.65000152587891</v>
+        <v>35.59999847412109</v>
       </c>
       <c r="I32" t="n">
-        <v>0.4207573452447473</v>
+        <v>0.4213483326664756</v>
       </c>
       <c r="J32" t="n">
         <v>14</v>
@@ -2027,10 +2027,10 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>21.02000045776367</v>
+        <v>21.36000061035156</v>
       </c>
       <c r="I34" t="n">
-        <v>1.189343456496754</v>
+        <v>1.170411951574777</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -2074,10 +2074,10 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>29</v>
+        <v>29.29999923706055</v>
       </c>
       <c r="I35" t="n">
-        <v>0.6724137931034483</v>
+        <v>0.6655290275685445</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -2168,10 +2168,10 @@
         </is>
       </c>
       <c r="H37" t="n">
-        <v>5.230000019073486</v>
+        <v>5.239999771118164</v>
       </c>
       <c r="I37" t="n">
-        <v>5.544933058171853</v>
+        <v>5.534351386777195</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -2215,10 +2215,10 @@
         </is>
       </c>
       <c r="H38" t="n">
-        <v>3.615999937057495</v>
+        <v>3.634000062942505</v>
       </c>
       <c r="I38" t="n">
-        <v>4.424778838082595</v>
+        <v>4.402861783949601</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -2262,10 +2262,10 @@
         </is>
       </c>
       <c r="H39" t="n">
-        <v>2.453999996185303</v>
+        <v>2.496000051498413</v>
       </c>
       <c r="I39" t="n">
-        <v>5.647921769170787</v>
+        <v>5.552884500815409</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -2309,10 +2309,10 @@
         </is>
       </c>
       <c r="H40" t="n">
-        <v>50.54000091552734</v>
+        <v>50.08000183105469</v>
       </c>
       <c r="I40" t="n">
-        <v>1.246537373540976</v>
+        <v>1.257987174452011</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -2356,10 +2356,10 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>6.34499979019165</v>
+        <v>6.340000152587891</v>
       </c>
       <c r="I41" t="n">
-        <v>2.206461853890326</v>
+        <v>2.208201839598603</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -2403,10 +2403,10 @@
         </is>
       </c>
       <c r="H42" t="n">
-        <v>17.39999961853027</v>
+        <v>16.95000076293945</v>
       </c>
       <c r="I42" t="n">
-        <v>4.482758718967629</v>
+        <v>4.601769704373353</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -2450,10 +2450,10 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>27.95999908447266</v>
+        <v>27.8799991607666</v>
       </c>
       <c r="I43" t="n">
-        <v>3.040057324150773</v>
+        <v>3.048780579578138</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -2497,10 +2497,10 @@
         </is>
       </c>
       <c r="H44" t="n">
-        <v>69.68000030517578</v>
+        <v>69.38999938964844</v>
       </c>
       <c r="I44" t="n">
-        <v>0.1291618823275391</v>
+        <v>0.1297016872627703</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -2587,10 +2587,10 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>6.188000202178955</v>
+        <v>6.251999855041504</v>
       </c>
       <c r="I46" t="n">
-        <v>2.929864157666956</v>
+        <v>2.899872108183157</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -2634,10 +2634,10 @@
         </is>
       </c>
       <c r="H47" t="n">
-        <v>8.609999656677246</v>
+        <v>8.670000076293945</v>
       </c>
       <c r="I47" t="n">
-        <v>3.019744603571084</v>
+        <v>2.998846571073376</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -2681,10 +2681,10 @@
         </is>
       </c>
       <c r="H48" t="n">
-        <v>9.982000350952148</v>
+        <v>10.13500022888184</v>
       </c>
       <c r="I48" t="n">
-        <v>2.774994893419113</v>
+        <v>2.73310304631893</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -2728,10 +2728,10 @@
         </is>
       </c>
       <c r="H49" t="n">
-        <v>1.019999980926514</v>
+        <v>1.039999961853027</v>
       </c>
       <c r="I49" t="n">
-        <v>1.32352943651404</v>
+        <v>1.298076970690103</v>
       </c>
       <c r="J49" t="n">
         <v>-7</v>
@@ -2775,10 +2775,10 @@
         </is>
       </c>
       <c r="H50" t="n">
-        <v>3.022000074386597</v>
+        <v>3.00600004196167</v>
       </c>
       <c r="I50" t="n">
-        <v>3.639973437867229</v>
+        <v>3.659347919643264</v>
       </c>
       <c r="J50" t="n">
         <v>-7</v>
@@ -2869,10 +2869,10 @@
         </is>
       </c>
       <c r="H52" t="n">
-        <v>2.940000057220459</v>
+        <v>2.990000009536743</v>
       </c>
       <c r="I52" t="n">
-        <v>5.442176764828622</v>
+        <v>5.351170551494067</v>
       </c>
       <c r="J52" t="n">
         <v>-14</v>
@@ -2916,10 +2916,10 @@
         </is>
       </c>
       <c r="H53" t="n">
-        <v>0.8450000286102295</v>
+        <v>0.8600000143051147</v>
       </c>
       <c r="I53" t="n">
-        <v>2.958579781484442</v>
+        <v>2.90697669583182</v>
       </c>
       <c r="J53" t="n">
         <v>-14</v>
@@ -2963,10 +2963,10 @@
         </is>
       </c>
       <c r="H54" t="n">
-        <v>27.14999961853027</v>
+        <v>27.5</v>
       </c>
       <c r="I54" t="n">
-        <v>4.088397847499079</v>
+        <v>4.036363636363636</v>
       </c>
       <c r="J54" t="n">
         <v>-18</v>
@@ -3010,10 +3010,10 @@
         </is>
       </c>
       <c r="H55" t="n">
-        <v>0.9039999842643738</v>
+        <v>0.8980000019073486</v>
       </c>
       <c r="I55" t="n">
-        <v>3.318584128561946</v>
+        <v>3.340757231211593</v>
       </c>
       <c r="J55" t="n">
         <v>-21</v>
@@ -3057,10 +3057,10 @@
         </is>
       </c>
       <c r="H56" t="n">
-        <v>0.4699999988079071</v>
+        <v>0.4659999907016754</v>
       </c>
       <c r="I56" t="n">
-        <v>4.893617033688609</v>
+        <v>4.935622416079441</v>
       </c>
       <c r="J56" t="n">
         <v>-21</v>
@@ -3151,10 +3151,10 @@
         </is>
       </c>
       <c r="H58" t="n">
-        <v>9.340000152587891</v>
+        <v>9.260000228881836</v>
       </c>
       <c r="I58" t="n">
-        <v>2.141327588143398</v>
+        <v>2.159827160437882</v>
       </c>
       <c r="J58" t="n">
         <v>-21</v>
@@ -3198,10 +3198,10 @@
         </is>
       </c>
       <c r="H59" t="n">
-        <v>2.390000104904175</v>
+        <v>2.369999885559082</v>
       </c>
       <c r="I59" t="n">
-        <v>7.531380422563494</v>
+        <v>7.594937075599819</v>
       </c>
       <c r="J59" t="n">
         <v>-28</v>
@@ -3245,10 +3245,10 @@
         </is>
       </c>
       <c r="H60" t="n">
-        <v>8.25</v>
+        <v>8.300000190734863</v>
       </c>
       <c r="I60" t="n">
-        <v>3.636363636363636</v>
+        <v>3.614457748264686</v>
       </c>
       <c r="J60" t="n">
         <v>-28</v>
@@ -3292,10 +3292,10 @@
         </is>
       </c>
       <c r="H61" t="n">
-        <v>17.17000007629395</v>
+        <v>16.95999908447266</v>
       </c>
       <c r="I61" t="n">
-        <v>1.45602794926697</v>
+        <v>1.474056683345472</v>
       </c>
       <c r="J61" t="n">
         <v>-28</v>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="H62" t="n">
-        <v>3.970000028610229</v>
+        <v>3.940000057220459</v>
       </c>
       <c r="I62" t="n">
-        <v>0.7556675008514305</v>
+        <v>0.7614213087388637</v>
       </c>
       <c r="J62" t="n">
         <v>-28</v>
@@ -3386,10 +3386,10 @@
         </is>
       </c>
       <c r="H63" t="n">
-        <v>4.46999979019165</v>
+        <v>4.449999809265137</v>
       </c>
       <c r="I63" t="n">
-        <v>3.355704855493265</v>
+        <v>3.370786661331805</v>
       </c>
       <c r="J63" t="n">
         <v>-28</v>
@@ -5251,163 +5251,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Stock</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Autostrade Meridionali S.p.A.</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>MARZOCCHI POMPE S.p.A.</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Half Year Preliminary Results</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Moncler S.p.A.</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Moncler S.p.A.</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Racing Force S.p.A.</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Half Year Preliminary Results</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Redelfi S.p.A.</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>2026-06-23</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Unicredit S.p.A.</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>VINCENZO ZUCCHI S.p.A.</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>2026-07-20</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>